--- a/sheets/대금율보/검수/이사도라.xlsx
+++ b/sheets/대금율보/검수/이사도라.xlsx
@@ -4526,8 +4526,7 @@
       <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="E4" s="25"/>
@@ -4553,8 +4552,7 @@
       <c r="K4" s="25"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="M4" s="25"/>
@@ -4562,8 +4560,7 @@
       <c r="O4" s="25"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="Q4" s="25"/>
@@ -4777,8 +4774,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="C8" s="26"/>
@@ -4792,8 +4788,7 @@
       <c r="E8" s="26"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="G8" s="26"/>
@@ -4807,8 +4802,7 @@
       <c r="I8" s="26"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="K8" s="26"/>
@@ -4816,16 +4810,11 @@
       <c r="M8" s="26"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="O8" s="26"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="26"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
@@ -5043,8 +5032,7 @@
       <c r="C12" s="24"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -5072,8 +5060,7 @@
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -5085,15 +5072,13 @@
       <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
       <c r="R12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="S12" s="22"/>

--- a/sheets/대금율보/검수/이사도라.xlsx
+++ b/sheets/대금율보/검수/이사도라.xlsx
@@ -4405,30 +4405,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="106.4" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="S3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="106.4" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="S4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="106.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="S5" s="26"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="106.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="106.4" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="S7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="106.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="S8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="106.4" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="106.4" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="S10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="106.4" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="S11" s="26"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="106.4" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="106.4" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="106.4" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -5213,6 +5213,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>